--- a/d890uv/Tracking CPS-Menu.xlsx
+++ b/d890uv/Tracking CPS-Menu.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andreas\Documents\codeplugs\d890uv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B358DC2D-9187-462B-A2BB-F908A76847B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{395A9AD9-B245-44EB-B996-D35CCB60A518}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="540" yWindow="348" windowWidth="12240" windowHeight="11472" xr2:uid="{BBF6BA9B-FEA4-4E33-A5D2-E76637C1E8DB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BBF6BA9B-FEA4-4E33-A5D2-E76637C1E8DB}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -628,8 +628,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{240F0127-2721-40E8-B69B-EE40E97A0DAD}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:E59"/>
+  <dimension ref="A1:E58"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" outlineLevelRow="2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.88671875" style="1" bestFit="1" customWidth="1"/>
@@ -700,7 +699,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
         <v>16</v>
       </c>
@@ -708,23 +707,23 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
         <v>18</v>
       </c>
       <c r="E8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B9" s="1" t="s">
         <v>24</v>
       </c>
@@ -732,7 +731,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="10" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B10" s="1" t="s">
         <v>25</v>
       </c>
@@ -740,7 +739,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="11" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
         <v>26</v>
       </c>
@@ -784,7 +783,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="15" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C15" t="s">
         <v>52</v>
       </c>
@@ -792,7 +791,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="16" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C16" t="s">
         <v>53</v>
       </c>
@@ -800,7 +799,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="2:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C17" t="s">
         <v>54</v>
       </c>
@@ -808,7 +807,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="18" spans="2:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C18" t="s">
         <v>55</v>
       </c>
@@ -816,7 +815,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="2:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C19" t="s">
         <v>56</v>
       </c>
@@ -846,7 +845,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="22" spans="2:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C22" t="s">
         <v>59</v>
       </c>
@@ -854,7 +853,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="23" spans="2:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C23" t="s">
         <v>60</v>
       </c>
@@ -862,7 +861,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="2:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C24" t="s">
         <v>61</v>
       </c>
@@ -870,7 +869,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="25" spans="2:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C25" t="s">
         <v>62</v>
       </c>
@@ -878,7 +877,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="2:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C26" t="s">
         <v>63</v>
       </c>
@@ -886,7 +885,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="2:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C27" t="s">
         <v>64</v>
       </c>
@@ -894,7 +893,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="28" spans="2:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C28" t="s">
         <v>65</v>
       </c>
@@ -924,7 +923,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="31" spans="2:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B31" s="1" t="s">
         <v>29</v>
       </c>
@@ -932,7 +931,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="32" spans="2:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B32" s="1" t="s">
         <v>30</v>
       </c>
@@ -940,7 +939,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="33" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B33" s="1" t="s">
         <v>31</v>
       </c>
@@ -959,7 +958,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B35" s="1" t="s">
         <v>33</v>
       </c>
@@ -1088,7 +1087,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="47" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B47" s="1" t="s">
         <v>41</v>
       </c>
@@ -1096,7 +1095,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="48" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B48" s="1" t="s">
         <v>42</v>
       </c>
@@ -1104,7 +1103,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="49" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B49" s="1" t="s">
         <v>43</v>
       </c>
@@ -1112,7 +1111,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="50" spans="1:5" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="C50" t="s">
         <v>44</v>
       </c>
@@ -1120,7 +1119,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="51" spans="1:5" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="C51" t="s">
         <v>45</v>
       </c>
@@ -1128,7 +1127,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="52" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>2</v>
       </c>
@@ -1136,7 +1135,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="53" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B53" s="1" t="s">
         <v>4</v>
       </c>
@@ -1144,7 +1143,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="54" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B54" s="1" t="s">
         <v>5</v>
       </c>
@@ -1152,7 +1151,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="55" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B55" s="1" t="s">
         <v>6</v>
       </c>
@@ -1160,7 +1159,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="56" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B56" s="1" t="s">
         <v>7</v>
       </c>
@@ -1168,7 +1167,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="57" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B57" s="1" t="s">
         <v>8</v>
       </c>
@@ -1176,7 +1175,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="58" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B58" s="1" t="s">
         <v>9</v>
       </c>
@@ -1184,15 +1183,8 @@
         <v>34</v>
       </c>
     </row>
-    <row r="59" spans="1:5" hidden="1" collapsed="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <autoFilter ref="D1:E59" xr:uid="{240F0127-2721-40E8-B69B-EE40E97A0DAD}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="x"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="D1:E59" xr:uid="{240F0127-2721-40E8-B69B-EE40E97A0DAD}"/>
   <conditionalFormatting sqref="E1:E1048576">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"Missing"</formula>

--- a/d890uv/Tracking CPS-Menu.xlsx
+++ b/d890uv/Tracking CPS-Menu.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andreas\Documents\codeplugs\d890uv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{395A9AD9-B245-44EB-B996-D35CCB60A518}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3122EC6D-A5D3-4235-B6DF-6727BF61452B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BBF6BA9B-FEA4-4E33-A5D2-E76637C1E8DB}"/>
+    <workbookView xWindow="9012" yWindow="456" windowWidth="12240" windowHeight="11472" xr2:uid="{BBF6BA9B-FEA4-4E33-A5D2-E76637C1E8DB}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -628,7 +628,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{240F0127-2721-40E8-B69B-EE40E97A0DAD}">
-  <dimension ref="A1:E58"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:E59"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" outlineLevelRow="2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.88671875" style="1" bestFit="1" customWidth="1"/>
@@ -699,7 +700,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
         <v>16</v>
       </c>
@@ -707,7 +708,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
         <v>17</v>
       </c>
@@ -715,7 +716,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
         <v>18</v>
       </c>
@@ -723,7 +724,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B9" s="1" t="s">
         <v>24</v>
       </c>
@@ -731,7 +732,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="10" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B10" s="1" t="s">
         <v>25</v>
       </c>
@@ -739,7 +740,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="11" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
         <v>26</v>
       </c>
@@ -783,7 +784,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="15" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C15" t="s">
         <v>52</v>
       </c>
@@ -791,7 +792,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="16" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C16" t="s">
         <v>53</v>
       </c>
@@ -799,7 +800,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C17" t="s">
         <v>54</v>
       </c>
@@ -807,7 +808,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="18" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C18" t="s">
         <v>55</v>
       </c>
@@ -815,7 +816,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C19" t="s">
         <v>56</v>
       </c>
@@ -831,7 +832,7 @@
         <v>47</v>
       </c>
       <c r="E20" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.3">
@@ -845,7 +846,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="22" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C22" t="s">
         <v>59</v>
       </c>
@@ -853,7 +854,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="23" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C23" t="s">
         <v>60</v>
       </c>
@@ -861,7 +862,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C24" t="s">
         <v>61</v>
       </c>
@@ -869,7 +870,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="25" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C25" t="s">
         <v>62</v>
       </c>
@@ -877,7 +878,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C26" t="s">
         <v>63</v>
       </c>
@@ -885,7 +886,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C27" t="s">
         <v>64</v>
       </c>
@@ -893,7 +894,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="28" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C28" t="s">
         <v>65</v>
       </c>
@@ -923,7 +924,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="31" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B31" s="1" t="s">
         <v>29</v>
       </c>
@@ -931,7 +932,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="32" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B32" s="1" t="s">
         <v>30</v>
       </c>
@@ -939,7 +940,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="33" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B33" s="1" t="s">
         <v>31</v>
       </c>
@@ -958,7 +959,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B35" s="1" t="s">
         <v>33</v>
       </c>
@@ -1087,7 +1088,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="47" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B47" s="1" t="s">
         <v>41</v>
       </c>
@@ -1095,7 +1096,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="48" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B48" s="1" t="s">
         <v>42</v>
       </c>
@@ -1103,7 +1104,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="49" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B49" s="1" t="s">
         <v>43</v>
       </c>
@@ -1111,7 +1112,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="50" spans="1:5" outlineLevel="2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="C50" t="s">
         <v>44</v>
       </c>
@@ -1119,7 +1120,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="51" spans="1:5" outlineLevel="2" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="C51" t="s">
         <v>45</v>
       </c>
@@ -1127,7 +1128,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>2</v>
       </c>
@@ -1135,7 +1136,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="53" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B53" s="1" t="s">
         <v>4</v>
       </c>
@@ -1143,7 +1144,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="54" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B54" s="1" t="s">
         <v>5</v>
       </c>
@@ -1151,7 +1152,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="55" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B55" s="1" t="s">
         <v>6</v>
       </c>
@@ -1159,7 +1160,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="56" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B56" s="1" t="s">
         <v>7</v>
       </c>
@@ -1167,7 +1168,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="57" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B57" s="1" t="s">
         <v>8</v>
       </c>
@@ -1175,7 +1176,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="58" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B58" s="1" t="s">
         <v>9</v>
       </c>
@@ -1183,8 +1184,15 @@
         <v>34</v>
       </c>
     </row>
+    <row r="59" spans="1:5" hidden="1" collapsed="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <autoFilter ref="D1:E59" xr:uid="{240F0127-2721-40E8-B69B-EE40E97A0DAD}"/>
+  <autoFilter ref="D1:E59" xr:uid="{240F0127-2721-40E8-B69B-EE40E97A0DAD}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="x"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <conditionalFormatting sqref="E1:E1048576">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"Missing"</formula>

--- a/d890uv/Tracking CPS-Menu.xlsx
+++ b/d890uv/Tracking CPS-Menu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andreas\Documents\codeplugs\d890uv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3122EC6D-A5D3-4235-B6DF-6727BF61452B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE54D5E3-C0C8-4CB6-81D5-B508EBF16808}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="9012" yWindow="456" windowWidth="12240" windowHeight="11472" xr2:uid="{BBF6BA9B-FEA4-4E33-A5D2-E76637C1E8DB}"/>
   </bookViews>
@@ -921,7 +921,7 @@
         <v>47</v>
       </c>
       <c r="E30" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="31" spans="2:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">

--- a/d890uv/Tracking CPS-Menu.xlsx
+++ b/d890uv/Tracking CPS-Menu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andreas\Documents\codeplugs\d890uv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE54D5E3-C0C8-4CB6-81D5-B508EBF16808}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C31AF47F-FA25-41CF-AA25-131C74B56851}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="9012" yWindow="456" windowWidth="12240" windowHeight="11472" xr2:uid="{BBF6BA9B-FEA4-4E33-A5D2-E76637C1E8DB}"/>
   </bookViews>
@@ -1063,7 +1063,7 @@
         <v>47</v>
       </c>
       <c r="E44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="45" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">

--- a/d890uv/Tracking CPS-Menu.xlsx
+++ b/d890uv/Tracking CPS-Menu.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andreas\Documents\codeplugs\d890uv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C31AF47F-FA25-41CF-AA25-131C74B56851}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F951D27-45D8-493E-B190-F4EA5E0ACB0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9012" yWindow="456" windowWidth="12240" windowHeight="11472" xr2:uid="{BBF6BA9B-FEA4-4E33-A5D2-E76637C1E8DB}"/>
+    <workbookView xWindow="3528" yWindow="60" windowWidth="16632" windowHeight="12180" xr2:uid="{BBF6BA9B-FEA4-4E33-A5D2-E76637C1E8DB}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Tabelle1!$D$1:$E$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Tabelle1!$D$1:$E$67</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Tabelle1!$A$1:$E$68</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="78">
   <si>
     <t>Common Settings</t>
   </si>
@@ -232,6 +233,36 @@
   </si>
   <si>
     <t>Digital Func</t>
+  </si>
+  <si>
+    <t>Analog Settings</t>
+  </si>
+  <si>
+    <t>General Settings</t>
+  </si>
+  <si>
+    <t>Digital Channels</t>
+  </si>
+  <si>
+    <t>Fixed Locations</t>
+  </si>
+  <si>
+    <t>Analog TX Freq</t>
+  </si>
+  <si>
+    <t>DMR Settings</t>
+  </si>
+  <si>
+    <t>Comments</t>
+  </si>
+  <si>
+    <t>"Digital Encryption" could not be set, "TX interrupt" crashed the CPS</t>
+  </si>
+  <si>
+    <t>"Analog APRS Report Frequency" can't be changed</t>
+  </si>
+  <si>
+    <t>"Compand" has no effect</t>
   </si>
 </sst>
 </file>
@@ -263,7 +294,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -271,11 +302,40 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -284,7 +344,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -629,7 +702,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{240F0127-2721-40E8-B69B-EE40E97A0DAD}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:E59"/>
+  <dimension ref="A1:F67"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" outlineLevelRow="2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.88671875" style="1" bestFit="1" customWidth="1"/>
@@ -637,556 +710,816 @@
     <col min="3" max="3" width="16.109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.21875" style="3" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="41.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+      <c r="F1" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="B2" s="5"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E2" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="1" t="s">
+    <row r="3" spans="1:6" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="5"/>
+      <c r="B3" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="C3" s="6"/>
+      <c r="D3" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="5"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="5"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F6" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="5"/>
+      <c r="B7" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="6"/>
+      <c r="D7" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="5"/>
+      <c r="B8" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="6"/>
+      <c r="D8" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="5"/>
+      <c r="B9" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="6"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="5"/>
+      <c r="B10" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="6"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="5"/>
+      <c r="B11" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="6"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="5"/>
+      <c r="B12" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="6"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="5"/>
+      <c r="B13" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="6"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="5"/>
+      <c r="B14" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" s="6"/>
+      <c r="D14" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="5"/>
+      <c r="B15" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" s="6"/>
+      <c r="D15" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E15" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E9" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E10" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="E11" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E12" t="s">
+    <row r="16" spans="1:6" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="5"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="5"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="5"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D18" s="7"/>
+      <c r="E18" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="5"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D19" s="7"/>
+      <c r="E19" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="5"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D20" s="7"/>
+      <c r="E20" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="5"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D21" s="7"/>
+      <c r="E21" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="5"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="D22" s="7"/>
+      <c r="E22" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="5"/>
+      <c r="B23" s="5"/>
+      <c r="C23" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="5"/>
+      <c r="B24" s="5"/>
+      <c r="C24" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="5"/>
+      <c r="B25" s="5"/>
+      <c r="C25" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D25" s="7"/>
+      <c r="E25" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="5"/>
+      <c r="B26" s="5"/>
+      <c r="C26" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="D26" s="7"/>
+      <c r="E26" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="5"/>
+      <c r="B27" s="5"/>
+      <c r="C27" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D27" s="7"/>
+      <c r="E27" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="5"/>
+      <c r="B28" s="5"/>
+      <c r="C28" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="D28" s="7"/>
+      <c r="E28" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="5"/>
+      <c r="B29" s="5"/>
+      <c r="C29" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D29" s="7"/>
+      <c r="E29" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="5"/>
+      <c r="B30" s="5"/>
+      <c r="C30" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D30" s="7"/>
+      <c r="E30" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="5"/>
+      <c r="B31" s="5"/>
+      <c r="C31" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="D31" s="7"/>
+      <c r="E31" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C13" t="s">
-        <v>50</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E13" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C14" t="s">
-        <v>51</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E14" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C15" t="s">
-        <v>52</v>
-      </c>
-      <c r="E15" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C16" t="s">
-        <v>53</v>
-      </c>
-      <c r="E16" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="17" spans="2:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C17" t="s">
-        <v>54</v>
-      </c>
-      <c r="E17" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="18" spans="2:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C18" t="s">
-        <v>55</v>
-      </c>
-      <c r="E18" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="19" spans="2:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C19" t="s">
-        <v>56</v>
-      </c>
-      <c r="E19" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="20" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C20" t="s">
-        <v>57</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E20" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="21" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C21" t="s">
-        <v>58</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E21" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="22" spans="2:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C22" t="s">
-        <v>59</v>
-      </c>
-      <c r="E22" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="23" spans="2:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C23" t="s">
-        <v>60</v>
-      </c>
-      <c r="E23" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="24" spans="2:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C24" t="s">
-        <v>61</v>
-      </c>
-      <c r="E24" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="25" spans="2:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C25" t="s">
-        <v>62</v>
-      </c>
-      <c r="E25" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="26" spans="2:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C26" t="s">
-        <v>63</v>
-      </c>
-      <c r="E26" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="27" spans="2:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C27" t="s">
-        <v>64</v>
-      </c>
-      <c r="E27" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="28" spans="2:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C28" t="s">
-        <v>65</v>
-      </c>
-      <c r="E28" t="s">
+    <row r="32" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="5"/>
+      <c r="B32" s="5"/>
+      <c r="C32" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="5"/>
+      <c r="B33" s="5"/>
+      <c r="C33" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="5"/>
+      <c r="B34" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C34" s="6"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="5"/>
+      <c r="B35" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C35" s="6"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="5"/>
+      <c r="B36" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C36" s="6"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="5"/>
+      <c r="B37" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C37" s="6"/>
+      <c r="D37" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="5"/>
+      <c r="B38" s="5"/>
+      <c r="C38" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="5"/>
+      <c r="B39" s="5"/>
+      <c r="C39" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="5"/>
+      <c r="B40" s="5"/>
+      <c r="C40" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="D40" s="7"/>
+      <c r="E40" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="5"/>
+      <c r="B41" s="5"/>
+      <c r="C41" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="D41" s="7"/>
+      <c r="E41" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="5"/>
+      <c r="B42" s="5"/>
+      <c r="C42" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="5"/>
+      <c r="B43" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C43" s="6"/>
+      <c r="D43" s="7"/>
+      <c r="E43" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A44" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B44" s="5"/>
+      <c r="C44" s="6"/>
+      <c r="D44" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E44" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="29" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C29" t="s">
-        <v>66</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E29" t="s">
+    <row r="45" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="5"/>
+      <c r="B45" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C45" s="6"/>
+      <c r="D45" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E45" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="5"/>
+      <c r="B46" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C46" s="6"/>
+      <c r="D46" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="5"/>
+      <c r="B47" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C47" s="6"/>
+      <c r="D47" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E47" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="5"/>
+      <c r="B48" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C48" s="6"/>
+      <c r="D48" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E48" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="30" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C30" t="s">
-        <v>67</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E30" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="31" spans="2:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E31" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="32" spans="2:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E32" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E33" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E34" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E35" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A36" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E36" t="s">
+    <row r="49" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="5"/>
+      <c r="B49" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C49" s="6"/>
+      <c r="D49" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E49" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="37" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E37" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="B38" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E38" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="B39" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E39" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="B40" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E40" t="s">
+    <row r="50" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="5"/>
+      <c r="B50" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C50" s="6"/>
+      <c r="D50" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E50" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="5"/>
+      <c r="B51" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C51" s="6"/>
+      <c r="D51" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E51" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="5"/>
+      <c r="B52" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C52" s="6"/>
+      <c r="D52" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E52" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="5"/>
+      <c r="B53" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C53" s="6"/>
+      <c r="D53" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E53" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="5"/>
+      <c r="B54" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C54" s="6"/>
+      <c r="D54" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E54" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="5"/>
+      <c r="B55" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C55" s="6"/>
+      <c r="D55" s="7"/>
+      <c r="E55" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="5"/>
+      <c r="B56" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C56" s="6"/>
+      <c r="D56" s="7"/>
+      <c r="E56" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="5"/>
+      <c r="B57" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C57" s="6"/>
+      <c r="D57" s="7"/>
+      <c r="E57" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A58" s="5"/>
+      <c r="B58" s="5"/>
+      <c r="C58" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D58" s="7"/>
+      <c r="E58" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A59" s="5"/>
+      <c r="B59" s="5"/>
+      <c r="C59" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D59" s="7"/>
+      <c r="E59" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B60" s="5"/>
+      <c r="C60" s="6"/>
+      <c r="D60" s="7"/>
+      <c r="E60" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="41" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="B41" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E41" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="B42" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E42" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="B43" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E43" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="B44" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E44" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="B45" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E45" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="B46" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E46" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="B47" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E47" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="B48" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E48" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="B49" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E49" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="C50" t="s">
-        <v>44</v>
-      </c>
-      <c r="E50" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="C51" t="s">
-        <v>45</v>
-      </c>
-      <c r="E51" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E52" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="B53" s="1" t="s">
+    <row r="61" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="5"/>
+      <c r="B61" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="E53" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="B54" s="1" t="s">
+      <c r="C61" s="6"/>
+      <c r="D61" s="7"/>
+      <c r="E61" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="5"/>
+      <c r="B62" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="E54" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="B55" s="1" t="s">
+      <c r="C62" s="6"/>
+      <c r="D62" s="7"/>
+      <c r="E62" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="5"/>
+      <c r="B63" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E55" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="B56" s="1" t="s">
+      <c r="C63" s="6"/>
+      <c r="D63" s="7"/>
+      <c r="E63" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="5"/>
+      <c r="B64" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E56" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="B57" s="1" t="s">
+      <c r="C64" s="6"/>
+      <c r="D64" s="7"/>
+      <c r="E64" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="5"/>
+      <c r="B65" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E57" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="B58" s="1" t="s">
+      <c r="C65" s="6"/>
+      <c r="D65" s="7"/>
+      <c r="E65" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="8"/>
+      <c r="B66" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E58" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" hidden="1" collapsed="1" x14ac:dyDescent="0.3"/>
+      <c r="C66" s="9"/>
+      <c r="D66" s="10"/>
+      <c r="E66" s="9" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" hidden="1" collapsed="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <autoFilter ref="D1:E59" xr:uid="{240F0127-2721-40E8-B69B-EE40E97A0DAD}">
+  <autoFilter ref="D1:E67" xr:uid="{240F0127-2721-40E8-B69B-EE40E97A0DAD}">
     <filterColumn colId="0">
       <filters>
         <filter val="x"/>
@@ -1205,6 +1538,6 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/d890uv/Tracking CPS-Menu.xlsx
+++ b/d890uv/Tracking CPS-Menu.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andreas\Documents\codeplugs\d890uv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F951D27-45D8-493E-B190-F4EA5E0ACB0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{304D3183-78EF-4F06-9B8D-4DE283A18A38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3528" yWindow="60" windowWidth="16632" windowHeight="12180" xr2:uid="{BBF6BA9B-FEA4-4E33-A5D2-E76637C1E8DB}"/>
+    <workbookView xWindow="10512" yWindow="60" windowWidth="12528" windowHeight="12180" xr2:uid="{BBF6BA9B-FEA4-4E33-A5D2-E76637C1E8DB}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -1167,7 +1167,7 @@
         <v>47</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
     </row>
     <row r="38" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
@@ -1180,7 +1180,7 @@
         <v>47</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="39" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
@@ -1193,7 +1193,7 @@
         <v>47</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="40" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="D41" s="7"/>
       <c r="E41" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="42" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
@@ -1228,7 +1228,7 @@
         <v>47</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="43" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">

--- a/d890uv/Tracking CPS-Menu.xlsx
+++ b/d890uv/Tracking CPS-Menu.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andreas\Documents\codeplugs\d890uv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{304D3183-78EF-4F06-9B8D-4DE283A18A38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{465EE304-457C-4696-A42E-A51468EBA9B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10512" yWindow="60" windowWidth="12528" windowHeight="12180" xr2:uid="{BBF6BA9B-FEA4-4E33-A5D2-E76637C1E8DB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BBF6BA9B-FEA4-4E33-A5D2-E76637C1E8DB}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -1382,7 +1382,7 @@
         <v>47</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="55" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">

--- a/d890uv/Tracking CPS-Menu.xlsx
+++ b/d890uv/Tracking CPS-Menu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andreas\Documents\codeplugs\d890uv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{465EE304-457C-4696-A42E-A51468EBA9B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5802EFD-F7D8-43C2-97AF-31CD1C87B906}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BBF6BA9B-FEA4-4E33-A5D2-E76637C1E8DB}"/>
   </bookViews>
@@ -1304,7 +1304,7 @@
         <v>47</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
     </row>
     <row r="49" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
@@ -1317,7 +1317,7 @@
         <v>47</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
     </row>
     <row r="50" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
@@ -1391,9 +1391,9 @@
         <v>41</v>
       </c>
       <c r="C55" s="6"/>
-      <c r="D55" s="7"/>
+      <c r="D55" s="11"/>
       <c r="E55" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="56" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
